--- a/LookupTable.xlsx
+++ b/LookupTable.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Programming\Hackathons\uidai_data_hack_2026\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\OneDrive\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4426317-10B3-4140-A4D2-DDC9F8D3AFC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6144C7E8-9DFE-46EF-8ACA-BE44815D5C7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1BB9DF1D-FA51-4892-9C26-CE2B44E49FD2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{C65BA773-D0F6-4A03-8967-B9765EC77135}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -34,99 +34,441 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
-  <si>
-    <t>RawValue</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="145">
+  <si>
+    <t>K.V.Rangareddy</t>
+  </si>
+  <si>
+    <t>Rangareddy</t>
+  </si>
+  <si>
+    <t>K.v. Rangareddy</t>
+  </si>
+  <si>
+    <t>Mahabub Nagar</t>
+  </si>
+  <si>
+    <t>Mahabubnagar</t>
+  </si>
+  <si>
+    <t>Mahbubnagar</t>
+  </si>
+  <si>
+    <t>N. T. R</t>
+  </si>
+  <si>
+    <t>N T R</t>
+  </si>
+  <si>
+    <t>Rangareddi</t>
+  </si>
+  <si>
+    <t>Ananthapur</t>
+  </si>
+  <si>
+    <t>Anantapur</t>
+  </si>
+  <si>
+    <t>Eluru</t>
+  </si>
+  <si>
+    <t>Anakapalli</t>
+  </si>
+  <si>
+    <t>Y. S. R</t>
+  </si>
+  <si>
+    <t>Y S R</t>
+  </si>
+  <si>
+    <t>Darjiling</t>
+  </si>
+  <si>
+    <t>Darjeeling</t>
+  </si>
+  <si>
+    <t>Haora</t>
+  </si>
+  <si>
+    <t>Howrah</t>
+  </si>
+  <si>
+    <t>Koch Bihar</t>
+  </si>
+  <si>
+    <t>Cooch Behar</t>
+  </si>
+  <si>
+    <t>Puruliya</t>
+  </si>
+  <si>
+    <t>Purulia</t>
+  </si>
+  <si>
+    <t>South Twenty Four Parganas</t>
+  </si>
+  <si>
+    <t>South 24 Parganas</t>
+  </si>
+  <si>
+    <t>Hugli</t>
+  </si>
+  <si>
+    <t>Jalpaiguri</t>
+  </si>
+  <si>
+    <t>Medinipur</t>
+  </si>
+  <si>
+    <t>Midnapore</t>
+  </si>
+  <si>
+    <t>West Medinipur</t>
+  </si>
+  <si>
+    <t>West Midnapore</t>
+  </si>
+  <si>
+    <t>Hawrah</t>
+  </si>
+  <si>
+    <t>South 24 Pargana</t>
+  </si>
+  <si>
+    <t>South 24 Paganas</t>
+  </si>
+  <si>
+    <t>East Midnapur</t>
+  </si>
+  <si>
+    <t>East Midnapore</t>
+  </si>
+  <si>
+    <t>North Twenty Four Parganas</t>
+  </si>
+  <si>
+    <t>North 24 Parganas</t>
+  </si>
+  <si>
+    <t>Barddhaman</t>
+  </si>
+  <si>
+    <t>Bardhaman</t>
+  </si>
+  <si>
+    <t>Bagalkot *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bagalkot </t>
+  </si>
+  <si>
+    <t>Bengaluru South</t>
+  </si>
+  <si>
+    <t>Ramanagara</t>
+  </si>
+  <si>
+    <t>Chickmagalur</t>
+  </si>
+  <si>
+    <t>Chikmagalur</t>
+  </si>
+  <si>
+    <t>Chikkamagaluru</t>
+  </si>
+  <si>
+    <t>Bengaluru Rural</t>
+  </si>
+  <si>
+    <t>Banglore Rural</t>
+  </si>
+  <si>
+    <t>Bijapur(KAR)</t>
+  </si>
+  <si>
+    <t>Bijapur(Kar)</t>
+  </si>
+  <si>
+    <t>Gadag *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gadag </t>
+  </si>
+  <si>
+    <t>Haveri *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haveri </t>
+  </si>
+  <si>
+    <t>Chamarajanagar</t>
+  </si>
+  <si>
+    <t>Udupi *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Udupi </t>
+  </si>
+  <si>
+    <t>Chamarajanagar *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chamarajanagar </t>
+  </si>
+  <si>
+    <t>Kanniyakumari</t>
+  </si>
+  <si>
+    <t>Kanyakumari</t>
+  </si>
+  <si>
+    <t>Ahmadabad</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Arvalli</t>
+  </si>
+  <si>
+    <t>Aravalli</t>
+  </si>
+  <si>
+    <t>Nandurbar *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nandurbar </t>
+  </si>
+  <si>
+    <t>Washim *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Washim </t>
+  </si>
+  <si>
+    <t>Gondiya *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gondiya </t>
+  </si>
+  <si>
+    <t>Ahmadnagar</t>
+  </si>
+  <si>
+    <t>Ahmednagar</t>
+  </si>
+  <si>
+    <t>Hingoli *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hingoli </t>
+  </si>
+  <si>
+    <t>Chatrapati Sambhaji Nagar</t>
+  </si>
+  <si>
+    <t>Chhatrapati Sambhajinagar</t>
+  </si>
+  <si>
+    <t>Raigad</t>
+  </si>
+  <si>
+    <t>Ahmed Nagar</t>
+  </si>
+  <si>
+    <t>Anugul</t>
+  </si>
+  <si>
+    <t>Angul</t>
+  </si>
+  <si>
+    <t>JAJPUR</t>
+  </si>
+  <si>
+    <t>Jajpur</t>
+  </si>
+  <si>
+    <t>Anugal</t>
+  </si>
+  <si>
+    <t>Bara Banki</t>
+  </si>
+  <si>
+    <t>Barabanki</t>
+  </si>
+  <si>
+    <t>Bulandshahar</t>
+  </si>
+  <si>
+    <t>Bulandshahr</t>
+  </si>
+  <si>
+    <t>Kushinagar *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kushinagar </t>
+  </si>
+  <si>
+    <t>Allahabad</t>
+  </si>
+  <si>
+    <t>Prayagraj</t>
+  </si>
+  <si>
+    <t>Farrukhabad</t>
+  </si>
+  <si>
+    <t>Jyotiba Phule Nagar</t>
+  </si>
+  <si>
+    <t>Amroha</t>
+  </si>
+  <si>
+    <t>Shrawasti</t>
+  </si>
+  <si>
+    <t>Shravasti</t>
+  </si>
+  <si>
+    <t>Chandauli *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Chandauli </t>
+  </si>
+  <si>
+    <t>Mahoba *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mahoba </t>
+  </si>
+  <si>
+    <t>Gautam Buddha Nagar *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gautam Buddha Nagar </t>
+  </si>
+  <si>
+    <t>Khordha  *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Khordha </t>
+  </si>
+  <si>
+    <t>Anugul  *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Angul </t>
+  </si>
+  <si>
+    <t>S.A.S Nagar(Mohali)</t>
+  </si>
+  <si>
+    <t>Mohali</t>
+  </si>
+  <si>
+    <t>SAS Nagar (Mohali)</t>
+  </si>
+  <si>
+    <t>Medchal malkajgiri</t>
+  </si>
+  <si>
+    <t>Medchal-Malkajgiri</t>
+  </si>
+  <si>
+    <t>Yadadri.</t>
+  </si>
+  <si>
+    <t>Yadadri</t>
+  </si>
+  <si>
+    <t>Aurangabad(bh)</t>
+  </si>
+  <si>
+    <t>Aurangabad</t>
+  </si>
+  <si>
+    <t>Harda *</t>
+  </si>
+  <si>
+    <t>Harda</t>
+  </si>
+  <si>
+    <t>Lahul &amp; Spiti</t>
+  </si>
+  <si>
+    <t>Lahaul &amp; Spiti</t>
+  </si>
+  <si>
+    <t>Garhwa *</t>
+  </si>
+  <si>
+    <t>Garhwa</t>
+  </si>
+  <si>
+    <t>Palamau</t>
+  </si>
+  <si>
+    <t>Palamu</t>
+  </si>
+  <si>
+    <t>Kodarma</t>
+  </si>
+  <si>
+    <t>Koderma</t>
+  </si>
+  <si>
+    <t>Bokaro *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bokaro </t>
+  </si>
+  <si>
+    <t>Jhunjhunun</t>
+  </si>
+  <si>
+    <t>Jhunjhunu</t>
+  </si>
+  <si>
+    <t>Gaurela-pendra-marwahi</t>
+  </si>
+  <si>
+    <t>Gaurela-Pendra-Marwahi</t>
+  </si>
+  <si>
+    <t>Baramula</t>
+  </si>
+  <si>
+    <t>Baramulla</t>
+  </si>
+  <si>
+    <t>Dhalai  *</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dhalai </t>
+  </si>
+  <si>
+    <t>Shi-yomi</t>
+  </si>
+  <si>
+    <t>Shi-Yomi</t>
+  </si>
+  <si>
+    <t>Leh (ladakh)</t>
+  </si>
+  <si>
+    <t>Leh (Ladakh)</t>
+  </si>
+  <si>
+    <t>Nicobars</t>
+  </si>
+  <si>
+    <t>Nicobar</t>
+  </si>
+  <si>
+    <t>RawData</t>
   </si>
   <si>
     <t>CleanValue</t>
-  </si>
-  <si>
-    <t>Andaman And Nicobar Islands</t>
-  </si>
-  <si>
-    <t>Andaman &amp; Nicobar Islands</t>
-  </si>
-  <si>
-    <t>Chhatisgarh</t>
-  </si>
-  <si>
-    <t>Chhattisgarh</t>
-  </si>
-  <si>
-    <t>Dadra And Nagar Haveli</t>
-  </si>
-  <si>
-    <t>Dadra &amp; Nagar Haveli</t>
-  </si>
-  <si>
-    <t>Daman And Diu</t>
-  </si>
-  <si>
-    <t>Daman &amp; Diu</t>
-  </si>
-  <si>
-    <t>Jammu And Kashmir</t>
-  </si>
-  <si>
-    <t>Jammu &amp; Kashmir</t>
-  </si>
-  <si>
-    <t>Orissa</t>
-  </si>
-  <si>
-    <t>Odisha</t>
-  </si>
-  <si>
-    <t>Puducherry</t>
-  </si>
-  <si>
-    <t>Pondicherry</t>
-  </si>
-  <si>
-    <t>Tamilnadu</t>
-  </si>
-  <si>
-    <t>Tamil Nadu</t>
-  </si>
-  <si>
-    <t>Uttaranchal</t>
-  </si>
-  <si>
-    <t>Uttarakhand</t>
-  </si>
-  <si>
-    <t>West Bangal</t>
-  </si>
-  <si>
-    <t>West Bengal</t>
-  </si>
-  <si>
-    <t>Westbengal</t>
-  </si>
-  <si>
-    <t>Ahmadnagar</t>
-  </si>
-  <si>
-    <t>Ahmed Nagar</t>
-  </si>
-  <si>
-    <t>Ananthapur</t>
-  </si>
-  <si>
-    <t>Anantapur</t>
-  </si>
-  <si>
-    <t>Ananthapuramu</t>
-  </si>
-  <si>
-    <t>Anugul *</t>
-  </si>
-  <si>
-    <t>Anugal</t>
-  </si>
-  <si>
-    <t>Anugul</t>
   </si>
 </sst>
 </file>
@@ -162,11 +504,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -480,152 +819,655 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BA6A66C-A5E2-4AA4-BC0B-FBA991E7DF2A}">
-  <dimension ref="A1:B17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B498597-627A-4AC2-BA16-AD7AA9281CB2}">
+  <dimension ref="A1:B80"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="14" style="1" customWidth="1"/>
+    <col min="1" max="1" width="24.5546875" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B3" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="B4" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="1" t="s">
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="B6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="B7" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+      <c r="B8" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="1" t="s">
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+      <c r="B9" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="1" t="s">
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+      <c r="B11" t="s">
         <v>14</v>
       </c>
-      <c r="B8" s="1" t="s">
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+      <c r="B12" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="1" t="s">
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="B13" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="1" t="s">
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="B14" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="1" t="s">
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="B15" t="s">
         <v>22</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
         <v>23</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B16" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A17" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B17" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A18" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="30" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="B18" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A19" t="s">
         <v>27</v>
       </c>
-      <c r="B15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B19" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A20" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>30</v>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>31</v>
+      </c>
+      <c r="B21" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>32</v>
+      </c>
+      <c r="B22" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>34</v>
+      </c>
+      <c r="B23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>36</v>
+      </c>
+      <c r="B24" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>40</v>
+      </c>
+      <c r="B26" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>42</v>
+      </c>
+      <c r="B27" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
+        <v>44</v>
+      </c>
+      <c r="B28" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
+        <v>47</v>
+      </c>
+      <c r="B30" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>49</v>
+      </c>
+      <c r="B31" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
+        <v>51</v>
+      </c>
+      <c r="B32" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
+        <v>53</v>
+      </c>
+      <c r="B33" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
+        <v>55</v>
+      </c>
+      <c r="B34" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>56</v>
+      </c>
+      <c r="B35" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A36" t="s">
+        <v>58</v>
+      </c>
+      <c r="B36" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A37" t="s">
+        <v>60</v>
+      </c>
+      <c r="B37" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A38" t="s">
+        <v>62</v>
+      </c>
+      <c r="B38" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>64</v>
+      </c>
+      <c r="B39" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A40" t="s">
+        <v>66</v>
+      </c>
+      <c r="B40" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A41" t="s">
+        <v>68</v>
+      </c>
+      <c r="B41" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A42" t="s">
+        <v>70</v>
+      </c>
+      <c r="B42" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A43" t="s">
+        <v>72</v>
+      </c>
+      <c r="B43" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>74</v>
+      </c>
+      <c r="B44" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A45" t="s">
+        <v>76</v>
+      </c>
+      <c r="B45" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A46" t="s">
+        <v>78</v>
+      </c>
+      <c r="B46" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A47" t="s">
+        <v>79</v>
+      </c>
+      <c r="B47" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A48" t="s">
+        <v>80</v>
+      </c>
+      <c r="B48" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A49" t="s">
+        <v>82</v>
+      </c>
+      <c r="B49" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A50" t="s">
+        <v>84</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A51" t="s">
+        <v>85</v>
+      </c>
+      <c r="B51" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>87</v>
+      </c>
+      <c r="B52" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A53" t="s">
+        <v>89</v>
+      </c>
+      <c r="B53" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A54" t="s">
+        <v>91</v>
+      </c>
+      <c r="B54" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A55" t="s">
+        <v>93</v>
+      </c>
+      <c r="B55" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A56" t="s">
+        <v>94</v>
+      </c>
+      <c r="B56" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
+        <v>96</v>
+      </c>
+      <c r="B57" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A58" t="s">
+        <v>98</v>
+      </c>
+      <c r="B58" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A59" t="s">
+        <v>100</v>
+      </c>
+      <c r="B59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A60" t="s">
+        <v>102</v>
+      </c>
+      <c r="B60" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A61" t="s">
+        <v>104</v>
+      </c>
+      <c r="B61" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A62" t="s">
+        <v>106</v>
+      </c>
+      <c r="B62" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A63" t="s">
+        <v>108</v>
+      </c>
+      <c r="B63" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A64" t="s">
+        <v>110</v>
+      </c>
+      <c r="B64" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A65" t="s">
+        <v>111</v>
+      </c>
+      <c r="B65" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A66" t="s">
+        <v>113</v>
+      </c>
+      <c r="B66" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A67" t="s">
+        <v>115</v>
+      </c>
+      <c r="B67" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A68" t="s">
+        <v>117</v>
+      </c>
+      <c r="B68" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A69" t="s">
+        <v>119</v>
+      </c>
+      <c r="B69" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A70" t="s">
+        <v>121</v>
+      </c>
+      <c r="B70" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>123</v>
+      </c>
+      <c r="B71" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>125</v>
+      </c>
+      <c r="B72" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>127</v>
+      </c>
+      <c r="B73" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>129</v>
+      </c>
+      <c r="B74" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>131</v>
+      </c>
+      <c r="B75" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>133</v>
+      </c>
+      <c r="B76" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>135</v>
+      </c>
+      <c r="B77" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>137</v>
+      </c>
+      <c r="B78" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>139</v>
+      </c>
+      <c r="B79" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
+        <v>141</v>
+      </c>
+      <c r="B80" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>